--- a/frontend/public/templates/sample_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_subjective_upload.xlsx
@@ -26,9 +26,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="3">
@@ -54,28 +55,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="00000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,11 +438,11 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="22.8" customWidth="1" min="2" max="2"/>
-    <col width="10.8" customWidth="1" min="3" max="3"/>
-    <col width="34.8" customWidth="1" min="4" max="4"/>
-    <col width="49.2" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="152" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,27 +473,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>WRITTEN</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>APTITUDE</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>10</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Write a short note on AI.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AI is a branch of computer science...</t>
+      <c r="C2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Explain why effective communication is vital in a professional workspace.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Effective communication ensures clarity, reduces misunderstandings, fosters collaboration, and helps in achieving organizational goals efficiently.</t>
         </is>
       </c>
     </row>

--- a/frontend/public/templates/sample_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_subjective_upload.xlsx
@@ -26,10 +26,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,8 +40,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F96331"/>
-        <bgColor rgb="00F96331"/>
+        <fgColor rgb="00f96331"/>
+        <bgColor rgb="00f96331"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,12 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,9 +436,9 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="78" customWidth="1" min="4" max="4"/>
     <col width="152" customWidth="1" min="5" max="5"/>
   </cols>
@@ -473,25 +471,25 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>APTITUDE</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Explain why effective communication is vital in a professional workspace.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Effective communication ensures clarity, reduces misunderstandings, fosters collaboration, and helps in achieving organizational goals efficiently.</t>
         </is>

--- a/frontend/public/templates/sample_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_subjective_upload.xlsx
@@ -54,19 +54,30 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,14 +444,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
-    <col width="152" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,29 +481,159 @@
           <t>Model Answer</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Answer Explanation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>APTITUDE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WRITTEN</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Explain why effective communication is vital in a professional workspace.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Effective communication ensures clarity, reduces misunderstandings, fosters collaboration, and helps in achieving organizational goals efficiently.</t>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Explain the core principles of professional ethics in scenario 1.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Professional ethics in scenario 1 involve transparency, accountability, and integrity...</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Assessing conceptual clarity and ethical judgment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>WRITTEN</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Explain the core principles of professional ethics in scenario 2.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Professional ethics in scenario 2 involve transparency, accountability, and integrity...</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Assessing conceptual clarity and ethical judgment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>WRITTEN</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Explain the core principles of professional ethics in scenario 3.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Professional ethics in scenario 3 involve transparency, accountability, and integrity...</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Assessing conceptual clarity and ethical judgment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>WRITTEN</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Explain the core principles of professional ethics in scenario 4.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Professional ethics in scenario 4 involve transparency, accountability, and integrity...</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Assessing conceptual clarity and ethical judgment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WRITTEN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FRESHER</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Explain the core principles of professional ethics in scenario 5.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Professional ethics in scenario 5 involve transparency, accountability, and integrity...</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Assessing conceptual clarity and ethical judgment.</t>
         </is>
       </c>
     </row>

--- a/frontend/public/templates/sample_subjective_upload.xlsx
+++ b/frontend/public/templates/sample_subjective_upload.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,8 +55,13 @@
         <bgColor rgb="00f96331"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF96331"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -67,16 +83,57 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,194 +501,205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Question Id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Subject Code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Exam Level Code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Marks</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Question Text</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Model Answer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Answer Explanation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>WRITTEN</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D2" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Explain the core principles of professional ethics in scenario 1.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Professional ethics in scenario 1 involve transparency, accountability, and integrity...</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Assessing conceptual clarity and ethical judgment.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>WRITTEN</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="D3" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Explain the core principles of professional ethics in scenario 2.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Professional ethics in scenario 2 involve transparency, accountability, and integrity...</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Assessing conceptual clarity and ethical judgment.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>WRITTEN</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="D4" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Explain the core principles of professional ethics in scenario 3.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Professional ethics in scenario 3 involve transparency, accountability, and integrity...</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Assessing conceptual clarity and ethical judgment.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>WRITTEN</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="D5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Explain the core principles of professional ethics in scenario 4.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Professional ethics in scenario 4 involve transparency, accountability, and integrity...</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Assessing conceptual clarity and ethical judgment.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>WRITTEN</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>FRESHER</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="D6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Explain the core principles of professional ethics in scenario 5.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Professional ethics in scenario 5 involve transparency, accountability, and integrity...</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Assessing conceptual clarity and ethical judgment.</t>
         </is>
